--- a/public/images/products/list_products.xlsx
+++ b/public/images/products/list_products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Claude\Projects\biohacker-digital\public\images\products\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E8B1C49-0846-481E-B2E0-C9657C13FF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BA731A-1A0C-42C0-8351-3FC3EB8F5C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39780" yWindow="2496" windowWidth="17280" windowHeight="8880" xr2:uid="{96CA0E1B-D343-4270-BA77-1A4585D27D3C}"/>
+    <workbookView xWindow="57492" yWindow="72" windowWidth="29016" windowHeight="15696" xr2:uid="{96CA0E1B-D343-4270-BA77-1A4585D27D3C}"/>
   </bookViews>
   <sheets>
     <sheet name="products" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>id</t>
   </si>
@@ -56,7 +56,182 @@
     <t>image</t>
   </si>
   <si>
-    <t>https://www.amazon.ca/dp/</t>
+    <t>https://www.amazon.ca/dp/B08R6XRYVD</t>
+  </si>
+  <si>
+    <t>Dowsing rods is a sensitive tool that can be affected by the thought and air space, also will be affected by the external world and energy properties of different things.</t>
+  </si>
+  <si>
+    <t>Dowsing Rods, Divining Rods For Water Finding, Dowsing Pendulum For Gold Detection, Metal Detector L Rods Copper, Radiesthesia Tools</t>
+  </si>
+  <si>
+    <t>2 PCS Dowsing Rods, Durable Brass Tools Water Detector Measuring Instruments with Handles Copper Dowsing Divining Rods Detector for Ghost Hunting Tools, Divining Water, Treasure</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B09VKTJQD6</t>
+  </si>
+  <si>
+    <t>Application- The dowsing rods are usually applied to ghost , divining water, looking for lost things and so on; Retractable Dowsing Rod- Made of steel, it is easy to carry and stretch, and the center shaft design is flexible. It will be affected by the external world and properties of different things. It can be used to look for the vein, water, crypt, people or something else
+Usage- Hold the handle, make the pin turning freely, peace your heart at same ; Think nothing then tell the dowsing rod what you are looking for</t>
+  </si>
+  <si>
+    <t>RetractilDowsingRods.jpg</t>
+  </si>
+  <si>
+    <t>Solid Copper and Brass Dowsing Rods with Smooth Movement for Tracing Spiritual Energy Chi, Ghost Hunting, Water Divining, Finding Gold</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B08L36KW7F</t>
+  </si>
+  <si>
+    <t>DeluxDowingRods.jpg</t>
+  </si>
+  <si>
+    <t>Pendulum - Top Plaza Bronze Metal Copper Spiritual Point Pendulum for Divination Healing Dowsing Wicca Balancing Pointed Cone Pendant Pendulum</t>
+  </si>
+  <si>
+    <t>[ WHAT CAN PENDULUM DO ] This pendulum is perfect for divination, chakra testing and spiritual healing. tantrism, spiritualism and eradication of evil forces. Pendulum should be clean after each use to get best results.
+[ DOWSING PENDULUM ] Dowsing pendulum can help you make healthy Good choices and help you find things you have lost, your pendulum can help you make decisions about your career, relationships or future plans,and help you heal balance your identifying energy field.</t>
+  </si>
+  <si>
+    <t>Includes two dowsing rods each 13.5 x 4.5 inches. Free gliding handles provide more sensitivity for feeling movements.
+Made from highly conductive copper metal and brass. As a conductor of energy, it can provide a connection to the spiritual world and amplify the users thoughts.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B085VN1MW8</t>
+  </si>
+  <si>
+    <t>CopperPendulum.jpg</t>
+  </si>
+  <si>
+    <t>CopperDowsingRods.jpg</t>
+  </si>
+  <si>
+    <t>Kit Kakalote Copper Dowsing Rod,Divining Rods Copper and Dowsing Pendulum,Pendulum Pendant for Energy Healing, Divining Water(Size:16.14 inch)</t>
+  </si>
+  <si>
+    <t>【DOWAING ROD】: It borrows the magnetic field sensitivity of the human body to release the subtle induction through the physical reaction of the rod and turns it into a visible signal. People, looking for lost things, breaking good and bad, etc.
+【STABLE ROTATION】: The central axis is designed with flexible turning, and the angle can be adjusted according to needs, and the telescopic design is convenient to adjust the length. Popularly used in geography and geomantic feng shui, it is a must-have tool for kanyu masters.
+【L-SHAPED DESIGN】: The probe is designed in an L shape, which is easy to hold and comfortable to hold. The handle can be freely rotated and adjusted, which is convenient for the accurate progress of the investigation work.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0C5936W2Q</t>
+  </si>
+  <si>
+    <t>DowsingRods+Pendulum.jpg</t>
+  </si>
+  <si>
+    <t>Exploration Set 2 Copper Dowsing Rods, Pendulum, and Mat for Finding Water, Minerals, and Enhancing Energy Therapy</t>
+  </si>
+  <si>
+    <t>Complete Dowsing Set: Includes 2 telescopic 99.9% copper dowsing rods, 1 wooden pendulum pad, and 1 pendant-everything needed to begin dowsing practice right away.
+FIRST-RATE Pure Copper Construction: Crafted from 99.9% copper for optimal conductivity and responsiveness during dowsing , supporting intuitive exploration and energetic alignment.
+Portable &amp; Ready-to-Use Design: Lightweight telescopic rods extend and lock securely; compact pendulum pad folds easily-perfect for field use, meditation spaces, or on-the-go intuitive work.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0GMQZVCBL</t>
+  </si>
+  <si>
+    <t>CompleteDownsingSet.jpg</t>
+  </si>
+  <si>
+    <t>7.83Hz Frequency Generator For Healing, Adjustable 0.1HZ-100000Hz Sine Signals Generator, USB Schumann Wave Resonance Generator, Pulses Generator Requency Devices Sound Frequency Machine (Green)</t>
+  </si>
+  <si>
+    <t>【 Upgraded Resonance Generator 】- This frequency devices is a new version of eletechsup's adjustable generator, which uses a low-temperature drift crystal and a high-precision dedicated chip. This frequency generator can accurately output frequency and sine
+【 Stable and Accurate 】- The wave resonance generator operates at the default frequency of 7.83Hz, and the sine amplitude is stabilized at 3V, while the square amplitude is set at 5V. Such setting ensures the stability and accuracy of the output The digital circuit crystal oscillators frequency reference is more stable and have strong antiinterference ability.
+【 Adjustable Frequencies 】- This frequency generator for hearing not only outputs 7.83Hz, but also incorporates programmable frequency modulation technology, which can adjust the frequency in the ranges of 0.1HZ-100000HZ.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0DPMNTNVF</t>
+  </si>
+  <si>
+    <t>FrequencyGenerator.jpg</t>
+  </si>
+  <si>
+    <t>Orgonite Pyramid for EMF Protection and Negative Energy Protection | Natural Crystal Orgone Organite Pyramid (Healing Copper Coil)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B08J4317GN</t>
+  </si>
+  <si>
+    <t>PiramidOrgonite.jpg</t>
+  </si>
+  <si>
+    <t>TriField EMF Meter Model TF2</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B078T2R64C</t>
+  </si>
+  <si>
+    <t>Detects: Magnetic fields, electric fields, and RF (20 MHz–6 GHz; includes most 5G but not experimental millimeter waves). Does not detect radioactivity.
+Displays: Average field signal and peak levels, plus pulse indicator bar in the upper left for RF monitoring
+Measures: 4G and 5G cell phones, cell towers, WiFi routers, Bluetooth, AC Powerlines, and Smart Meters</t>
+  </si>
+  <si>
+    <t>TriFieldEMF_TF2.jpg</t>
+  </si>
+  <si>
+    <t>ERICKHILL EMF Meter, Rechargeable Digital Electromagnetic Field Radiation Detector Hand-held Digital LCD EMF Detector, Great Tester for Home EMF Inspections, Office, Ghost Hunting (RF Not Included)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B08BLJM28J</t>
+  </si>
+  <si>
+    <t>ERICKHILL_EMF_Meter.jpg</t>
+  </si>
+  <si>
+    <t>PRECISE MEASUREMENT: Equipped with a built-in electromagnetic radiation sensor, which can display the radiation value on the clear LCD digital display after processing by a control micro-chip.(Please use the front sensing area to slowly approach the electromagnetic radiation source to be measured. The effective/optimal measurement range is 0-30cm)Testing magnetic field radiation with optional units mG/uT, and the electric field with unitV/m.This EMF meter can not test the RF value.</t>
+  </si>
+  <si>
+    <t>Grounding Mat Cotton EMF Grounding Anti-Slip Mat Grounding Sleep Sheet with 15ft Earth Mat Cloud Bedding Pad for Stress Relief (Grey, 34.2x50 in)</t>
+  </si>
+  <si>
+    <t>High Quality: This cotton mat, grounding pad is crafted from cotton, embedded with 5% silver fibers and crafted through a quilting process. It offers a softer, skin-friendly, and more comfortable experience than traditional grounding mats.
+Multi-functional: This grounding mat is versatile and can be placed on your bed, floor, sofa, and more. It is available in two sizes, with the 34.2*50 IN version doubling as a grounding blanket. EMF Grounding Anti-Slip Mat Pad,Grounding Sleep Sheet with 15ft. Additionally, it serves as a comfortable quilt during the hot summer months.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0DGG9SY5Y</t>
+  </si>
+  <si>
+    <t>GroundingMatCottonEMF.jpg</t>
+  </si>
+  <si>
+    <t>GAYA Grounding Mat for Feet, Earthing Mat for Sleep Improvement, Back Pain Relief, Muscle Relaxation &amp; Stress Relief, Grounding Pads for Bed, Grounding Mats for Desk, Earth Grounding Pad (24''X16'')</t>
+  </si>
+  <si>
+    <t>ACHIEVE DEEP SLEEP AND PAIN RELIEF: Experience improved sleep, pain relief, and muscle relaxation with our 24x16 inches (40x60 cm) Grounding Mat. Perfect for a restful night on your bed grounding mat.
+SAFE &amp; TESTED - 100K OHM RESISTOR: Built-in resistor protects against electrical surges for safe daily use. Premium 3-layer construction: skin-friendly PU top, conductive carbon center, non-slip base. Quality-tested for reliable grounding performance. Designed for daily, long-term use</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0D846VMP2</t>
+  </si>
+  <si>
+    <t>GroundingMatforFeet.jpg</t>
+  </si>
+  <si>
+    <t>Grounding Mat for Bed (King/Queen/Full/Twin) - Earthing Grounding Pad, Soft Breathable Conductive Carbon Sleep Mat, Better Sleep &amp; Muscle Relaxation, Anti-Slip Durable, Easy Setup, Gift Box Included</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0DH79WW6X</t>
+  </si>
+  <si>
+    <t>SLEEP BETTER &amp; WAKE REFRESHED - ALL BED SIZES: Soft breathable earthing mat available in King (76x27"), Queen (60x27"), Full (54x27"), Twin (38x27"). Use under fitted sheet or on top. Customers report falling asleep faster and waking without muscle soreness.</t>
+  </si>
+  <si>
+    <t>GroundingMatforBed(King_Queen_Full_Twin).jpg</t>
+  </si>
+  <si>
+    <t>Grounding Bed Sheets with Silver Threads and Deep Pockets, Queen &amp; King - Extra Soft 95% Organic Cotton 5% Pure Silver, Improve Sleep &amp; Reduce Stress Earthing Sheets, Grounding Sheets</t>
+  </si>
+  <si>
+    <t>BETTER SLEEP &amp; NATURAL HEALING – Experience deeper sleep, reduced stress, and improved circulation with GAYA Grounding Sheets. Designed to reconnect you to the Earth’s natural energy, our grounding bed sheets promote overall well-being.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0DS57S2J1</t>
+  </si>
+  <si>
+    <t>GroundingBedSheets.jpg</t>
   </si>
 </sst>
 </file>
@@ -101,9 +276,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -439,138 +622,327 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92ADB5C5-5056-4759-9A16-E445611996FF}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.77734375" customWidth="1"/>
-    <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="68.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="40" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="144" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{25C8B4E5-DB19-40D0-AB58-DECE73272A86}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{1A965D54-C4EA-45F4-ACA6-4E564D476325}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{5CDE0745-B2AD-4EEC-8C9F-4047C7D6F617}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{8D2A5934-D35F-4298-A17F-3D1137EAE018}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{364445A0-34FB-4657-B12F-595AC541E726}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{00BAFE1A-9B40-4F6E-8345-3A626BDFAAC1}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{C2E9AD3F-53C8-4BE5-9C2D-1889EFA7C180}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{67B54AA8-877C-4EAC-896C-2CC3FDF87DDE}"/>
+    <hyperlink ref="B21" r:id="rId9" xr:uid="{4A9BD8E5-C796-4122-891A-628673EF3FB7}"/>
+    <hyperlink ref="B20" r:id="rId10" xr:uid="{B9D7C85B-D9A8-4957-8EDE-C751622A6D70}"/>
+    <hyperlink ref="B11" r:id="rId11" xr:uid="{3D133E37-B163-441B-A67C-92BA8EE0CE4C}"/>
+    <hyperlink ref="B10" r:id="rId12" xr:uid="{0564751A-A291-4356-BF85-D3CB3B358724}"/>
+    <hyperlink ref="B12" r:id="rId13" xr:uid="{5D344AE8-D80C-48CE-B721-96FF13589EF5}"/>
+    <hyperlink ref="B13" r:id="rId14" xr:uid="{1933D47A-642E-468E-9166-4D85EAE30B56}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/images/products/list_products.xlsx
+++ b/public/images/products/list_products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Claude\Projects\biohacker-digital\public\images\products\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BA731A-1A0C-42C0-8351-3FC3EB8F5C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F00DAEB-1A74-49DC-A810-C7597D21BFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57492" yWindow="72" windowWidth="29016" windowHeight="15696" xr2:uid="{96CA0E1B-D343-4270-BA77-1A4585D27D3C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="111">
   <si>
     <t>id</t>
   </si>
@@ -135,9 +135,6 @@
     <t>CompleteDownsingSet.jpg</t>
   </si>
   <si>
-    <t>7.83Hz Frequency Generator For Healing, Adjustable 0.1HZ-100000Hz Sine Signals Generator, USB Schumann Wave Resonance Generator, Pulses Generator Requency Devices Sound Frequency Machine (Green)</t>
-  </si>
-  <si>
     <t>【 Upgraded Resonance Generator 】- This frequency devices is a new version of eletechsup's adjustable generator, which uses a low-temperature drift crystal and a high-precision dedicated chip. This frequency generator can accurately output frequency and sine
 【 Stable and Accurate 】- The wave resonance generator operates at the default frequency of 7.83Hz, and the sine amplitude is stabilized at 3V, while the square amplitude is set at 5V. Such setting ensures the stability and accuracy of the output The digital circuit crystal oscillators frequency reference is more stable and have strong antiinterference ability.
 【 Adjustable Frequencies 】- This frequency generator for hearing not only outputs 7.83Hz, but also incorporates programmable frequency modulation technology, which can adjust the frequency in the ranges of 0.1HZ-100000HZ.</t>
@@ -232,6 +229,170 @@
   </si>
   <si>
     <t>GroundingBedSheets.jpg</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>Downsing</t>
+  </si>
+  <si>
+    <t>Grounding</t>
+  </si>
+  <si>
+    <t>7.83Hz Frequency Generator For Healing, Adjustable 0.1HZ-100000Hz Sine Signals Generator, USB Schumann Wave Resonance Generator, Pulses Generator Frequency Devices Sound Frequency Machine (Green)</t>
+  </si>
+  <si>
+    <t>Generator Frequency</t>
+  </si>
+  <si>
+    <t>EMF</t>
+  </si>
+  <si>
+    <t>Radon</t>
+  </si>
+  <si>
+    <t>Airthings 325 Corentium Home 2 Smart Digital Radon Detector - Portable and Easy-to-use Radon Testing with Bluetooth connectivity and Humidity &amp; Temperature Sensors</t>
+  </si>
+  <si>
+    <t>THE ORIGINAL RADON DETECTOR, UPDATED: The same proven accuracy as the best-selling original Corentium Home, now with Bluetooth connectivity and bonus temp and humidity sensors.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0F84C4ZZM</t>
+  </si>
+  <si>
+    <t>Airthings325SmartDigitalRadonDetector.jpg</t>
+  </si>
+  <si>
+    <t>Airthings Wave Radon - Smart Radon Detector with Humidity &amp; Temperature Sensor – Easy-to-Use – Accurate – No Lab Fees – Battery Operated - Free App</t>
+  </si>
+  <si>
+    <t>RADON DETECTOR: Radon is the number one cause of lung cancer among non-smokers and kills more than 6x the number of people than home fires and carbon monoxide poisoning combined
+CONTINUOUS MONITORING: Radon gas fluctuates daily and is highly dependent on many factors such as weather conditions. Long-term monitoring is crucial to take control, understand long-term exposure and minimize potential health effects</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B07WWV7K3K</t>
+  </si>
+  <si>
+    <t>AirthingsWaveRadon-SmartRadonDetector.jpg</t>
+  </si>
+  <si>
+    <t>Airthings View Radon 2989 - Radon Monitor (Radon, Humidity, Temp) with WiFi &amp; Calm Tech Display</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B09SQ64K7Q</t>
+  </si>
+  <si>
+    <t>AirthingsViewRadon2989-RadonMonitor.jpg</t>
+  </si>
+  <si>
+    <t>Health Canada estimates that about 16% of lung cancer deaths are related to being exposed to radon in the home. Radon exposure is the leading cause of lung cancer in non-smokers
+NEW RADON SENSOR TECHNOLOGY: our most accurate, robust and sustainably-designed radon sensor, also measuring humidity and temperature</t>
+  </si>
+  <si>
+    <t>HOUND-1011 Portable Radon Detector for Home, Lightweight, High-Accuracy Sensor, 45-Day Monitoring, Easy-to-Use Radon Tester for Short- &amp; Long-Term in pCi/L or Bq/m³, for Basement – Gray</t>
+  </si>
+  <si>
+    <t>Portable Radon Detector: AEGTEST HOUND-1011 is a compact, portable radon detector for continuous monitoring. It measures radon levels from 0.09 to 1000 pCi/L, supports switching between pCi/L and Bq/m³ units, ensuring reliable protection against harmful radon gas</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0F99C4X2G</t>
+  </si>
+  <si>
+    <t>HOUND-1011_PortableRadonDetector.jpg</t>
+  </si>
+  <si>
+    <t>Grounding Sheets King Size Deep Pocket 12% Silver Fiber 88% Organic Cotton, Grounding Fitted Earth Sheets with Grounding Cord (Gray, King - 78"x80"x15")</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0H26WGM34</t>
+  </si>
+  <si>
+    <t>High-Quality Materials: The grounding sheets are made of organic cotton and silver fiber. Both silver and cotton are pure natural materials. The two materials are blended according to a certain ratio. They have good conductivity and are very soft and comfortable, and are very skin-friendly. The interlaced silver fibers can maximize the contact area between the skin and the conductive fibers.</t>
+  </si>
+  <si>
+    <t>GroundingSheetsKingSize.jpg</t>
+  </si>
+  <si>
+    <t>Hike Footwear Theora Pro - Ergonomic Supportive &amp; Non-Slip Barefoot Shoes, Wide Toe Box &amp; Durable Sole, Breathable Ultralight, Walking, Hiking, Zero Drop Shoes for Women Men (Unisex)</t>
+  </si>
+  <si>
+    <t>Size Matters (And We Mean It!): Don't guess—watch our quick video for foolproof, step-by-step measuring instructions. Get the perfect fit, not a size surprise!
+Natural Gait: With every step, Theora Pro shoes strengthen your foot and leg muscles. Experience reduced body aches and support your journey to recovery from issues like plantar fasciitis.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0DG363GG1</t>
+  </si>
+  <si>
+    <t>GroundingShoes.jpg</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0G2H2WDG4</t>
+  </si>
+  <si>
+    <t>Hike Footwear Comforto Max – Ultra-Stretching &amp; Soft Barefoot Shoes | Lightweight Non-Slip &amp; Zero-Drop Sole Summer Boots | Minimalist Comfortable Walking Shoes for Women Men</t>
+  </si>
+  <si>
+    <t>Wide Toe Box for Natural Toe Splay – Allows your toes to spread freely for better balance, improved stability, and reduced pressure on the forefoot. Ideal for bunions, swelling, and sensitive feet.
+Zero-Drop Sole – Keeps the heel and forefoot on the same level, encouraging proper posture from the feet up. By aligning your spine and distributing pressure evenly, it can help relieve tension in the knees, hips, and lower back—especially useful for aging joints.</t>
+  </si>
+  <si>
+    <t>GroundingShoes2.jpg</t>
+  </si>
+  <si>
+    <t>Grounding Shoes with Copper,Waterproof Non-Slip Comfort Hike Shoe, Copper Hike Barefoot Shoes for Women Men</t>
+  </si>
+  <si>
+    <t>【Spacious Toe Box, Comfortable Fit】: Our features an enlarged toe box for ultimate comfort and freedom. The grounding barefoot shoes accommodate various foot shapes and sizes, providing an ergonomic fit that allows your toes to spread naturally and reduces pressure points.【Quick-drying, Water-repellent, Free to Walk】: The Hike Shoes Footwear Barefoot Womens innovative bottom drainage hole design can quickly drain the water in the shoe, keeping your feet dry and comfortable. The grounding shoes for women unique porous drainage system allows you to enjoy a true amphibious experience whether you are exploring streams, strolling on the beach, or traveling on rainy days</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0GRW9PFQH</t>
+  </si>
+  <si>
+    <t>GroundingShoes3.jpg</t>
+  </si>
+  <si>
+    <t>Gardner Bender GRT-3500 Standard Outlet Tester</t>
+  </si>
+  <si>
+    <t>Outlet Tester</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B000NBDTQI</t>
+  </si>
+  <si>
+    <t>Makes quick work out of any electrical project
+Compact ergonomic design
+Neon lamps indicate 6 common wiring conditions
+Tests standard 3-prong outlets
+Tests standard outlets, and extension cords</t>
+  </si>
+  <si>
+    <t>OutletTester.jpg</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B07VSRK68V</t>
+  </si>
+  <si>
+    <t>Hooga Grounding Mat for Sleep, Energy &amp; Pain Relief – 24" x 16" Conductive Carbon Pad with 15ft Grounding Cord – Indoor Earth Connection for Inflammation &amp; Recovery</t>
+  </si>
+  <si>
+    <t>Experience the Benefits of Grounding: Hooga grounding mat helps you reconnect with the Earth’s natural energy, promoting improved sleep, reduced pain, increased energy, and overall wellness through natural grounding technology.</t>
+  </si>
+  <si>
+    <t>HoogaGroundingMat.jpg</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0D9N6KP72</t>
+  </si>
+  <si>
+    <t>【3 IN 1 Precise Measurement】The EMF meter detector has built-in electromagnetic radiation sensor, which can display the radiation value on a clear LCD digital display by controlling the microchip. It can not only measures electric and magnetic fields, but also keenly measure the temperature in the environment</t>
+  </si>
+  <si>
+    <t>3 in 1 Rechargeable EMF Meter, Digital Electromagnetic Field Radiation Detector Portable Hand-held 2'' LCD EMF Detector for Home EMF Inspections, Office, Outdoor, Ghost Hunting</t>
+  </si>
+  <si>
+    <t>RechargeableEMFMeter.jpg</t>
   </si>
 </sst>
 </file>
@@ -622,17 +783,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92ADB5C5-5056-4759-9A16-E445611996FF}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="50.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="68.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="40" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="1"/>
+    <col min="2" max="2" width="36.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="68.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="40" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -640,16 +802,19 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -657,16 +822,19 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -674,16 +842,19 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -691,16 +862,19 @@
         <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -708,16 +882,19 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="144" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -725,16 +902,19 @@
         <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -742,190 +922,938 @@
         <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12">
+    </row>
+    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="3" t="s">
+      <c r="F13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="1" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="E14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14">
+    </row>
+    <row r="15" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15">
         <v>13</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="B15" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>14</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="B16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A17">
         <v>15</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="B17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>16</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="B18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>17</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="B19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>18</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="B20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
+    </row>
+    <row r="24" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="F24" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>39</v>
-      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C53" s="3"/>
+    </row>
+    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C54" s="3"/>
+    </row>
+    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C55" s="3"/>
+    </row>
+    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C57" s="3"/>
+    </row>
+    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C58" s="3"/>
+    </row>
+    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C61" s="3"/>
+    </row>
+    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C62" s="3"/>
+    </row>
+    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C63" s="3"/>
+    </row>
+    <row r="64" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C64" s="3"/>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C65" s="3"/>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C66" s="3"/>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C67" s="3"/>
+    </row>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C68" s="3"/>
+    </row>
+    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C69" s="3"/>
+    </row>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C70" s="3"/>
+    </row>
+    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C71" s="3"/>
+    </row>
+    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C72" s="3"/>
+    </row>
+    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C73" s="3"/>
+    </row>
+    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C74" s="3"/>
+    </row>
+    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C75" s="3"/>
+    </row>
+    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C76" s="3"/>
+    </row>
+    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C77" s="3"/>
+    </row>
+    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C78" s="3"/>
+    </row>
+    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C79" s="3"/>
+    </row>
+    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C80" s="3"/>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C81" s="3"/>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C82" s="3"/>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C83" s="3"/>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C84" s="3"/>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C85" s="3"/>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C86" s="3"/>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C87" s="3"/>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C88" s="3"/>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C89" s="3"/>
+    </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C90" s="3"/>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C91" s="3"/>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C92" s="3"/>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C93" s="3"/>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C94" s="3"/>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C95" s="3"/>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C96" s="3"/>
+    </row>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C97" s="3"/>
+    </row>
+    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C98" s="3"/>
+    </row>
+    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C99" s="3"/>
+    </row>
+    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C100" s="3"/>
+    </row>
+    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C101" s="3"/>
+    </row>
+    <row r="102" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C102" s="3"/>
+    </row>
+    <row r="103" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C103" s="3"/>
+    </row>
+    <row r="104" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C104" s="3"/>
+    </row>
+    <row r="105" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C105" s="3"/>
+    </row>
+    <row r="106" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C106" s="3"/>
+    </row>
+    <row r="107" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C107" s="3"/>
+    </row>
+    <row r="108" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C108" s="3"/>
+    </row>
+    <row r="109" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C109" s="3"/>
+    </row>
+    <row r="110" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C110" s="3"/>
+    </row>
+    <row r="111" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C111" s="3"/>
+    </row>
+    <row r="112" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C112" s="3"/>
+    </row>
+    <row r="113" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C113" s="3"/>
+    </row>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C114" s="3"/>
+    </row>
+    <row r="115" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C115" s="3"/>
+    </row>
+    <row r="116" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C116" s="3"/>
+    </row>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C117" s="3"/>
+    </row>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C118" s="3"/>
+    </row>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C119" s="3"/>
+    </row>
+    <row r="120" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C120" s="3"/>
+    </row>
+    <row r="121" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C121" s="3"/>
+    </row>
+    <row r="122" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C122" s="3"/>
+    </row>
+    <row r="123" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C123" s="3"/>
+    </row>
+    <row r="124" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C124" s="3"/>
+    </row>
+    <row r="125" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C125" s="3"/>
+    </row>
+    <row r="126" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C126" s="3"/>
+    </row>
+    <row r="127" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C127" s="3"/>
+    </row>
+    <row r="128" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C128" s="3"/>
+    </row>
+    <row r="129" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C129" s="3"/>
+    </row>
+    <row r="130" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C130" s="3"/>
+    </row>
+    <row r="131" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C131" s="3"/>
+    </row>
+    <row r="132" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C132" s="3"/>
+    </row>
+    <row r="133" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C133" s="3"/>
+    </row>
+    <row r="134" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C134" s="3"/>
+    </row>
+    <row r="135" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C135" s="3"/>
+    </row>
+    <row r="136" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C136" s="3"/>
+    </row>
+    <row r="137" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C137" s="3"/>
+    </row>
+    <row r="138" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C138" s="3"/>
+    </row>
+    <row r="139" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C139" s="3"/>
+    </row>
+    <row r="140" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C140" s="3"/>
+    </row>
+    <row r="141" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C141" s="3"/>
+    </row>
+    <row r="142" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C142" s="3"/>
+    </row>
+    <row r="143" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C143" s="3"/>
+    </row>
+    <row r="144" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C144" s="3"/>
+    </row>
+    <row r="145" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C145" s="3"/>
+    </row>
+    <row r="146" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C146" s="3"/>
+    </row>
+    <row r="147" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C147" s="3"/>
+    </row>
+    <row r="148" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C148" s="3"/>
+    </row>
+    <row r="149" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C149" s="3"/>
+    </row>
+    <row r="150" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C150" s="3"/>
+    </row>
+    <row r="151" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C151" s="3"/>
+    </row>
+    <row r="152" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C152" s="3"/>
+    </row>
+    <row r="153" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C153" s="3"/>
+    </row>
+    <row r="154" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C154" s="3"/>
+    </row>
+    <row r="155" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C155" s="3"/>
+    </row>
+    <row r="156" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C156" s="3"/>
+    </row>
+    <row r="157" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C157" s="3"/>
+    </row>
+    <row r="158" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C158" s="3"/>
+    </row>
+    <row r="159" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C159" s="3"/>
+    </row>
+    <row r="160" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C160" s="3"/>
+    </row>
+    <row r="161" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C161" s="3"/>
+    </row>
+    <row r="162" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C162" s="3"/>
+    </row>
+    <row r="163" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C163" s="3"/>
+    </row>
+    <row r="164" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C164" s="3"/>
+    </row>
+    <row r="165" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C165" s="3"/>
+    </row>
+    <row r="166" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C166" s="3"/>
+    </row>
+    <row r="167" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C167" s="3"/>
+    </row>
+    <row r="168" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C168" s="3"/>
+    </row>
+    <row r="169" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C169" s="3"/>
+    </row>
+    <row r="170" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C170" s="3"/>
+    </row>
+    <row r="171" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C171" s="3"/>
+    </row>
+    <row r="172" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C172" s="3"/>
+    </row>
+    <row r="173" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C173" s="3"/>
+    </row>
+    <row r="174" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C174" s="3"/>
+    </row>
+    <row r="175" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C175" s="3"/>
+    </row>
+    <row r="176" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C176" s="3"/>
+    </row>
+    <row r="177" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C177" s="3"/>
+    </row>
+    <row r="178" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C178" s="3"/>
+    </row>
+    <row r="179" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C179" s="3"/>
+    </row>
+    <row r="180" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C180" s="3"/>
+    </row>
+    <row r="181" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C181" s="3"/>
+    </row>
+    <row r="182" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C182" s="3"/>
+    </row>
+    <row r="183" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C183" s="3"/>
+    </row>
+    <row r="184" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C184" s="3"/>
+    </row>
+    <row r="185" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C185" s="3"/>
+    </row>
+    <row r="186" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C186" s="3"/>
+    </row>
+    <row r="187" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C187" s="3"/>
+    </row>
+    <row r="188" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C188" s="3"/>
+    </row>
+    <row r="189" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C189" s="3"/>
+    </row>
+    <row r="190" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C190" s="3"/>
+    </row>
+    <row r="191" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C191" s="3"/>
+    </row>
+    <row r="192" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C192" s="3"/>
+    </row>
+    <row r="193" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C193" s="3"/>
+    </row>
+    <row r="194" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C194" s="3"/>
+    </row>
+    <row r="195" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C195" s="3"/>
+    </row>
+    <row r="196" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C196" s="3"/>
+    </row>
+    <row r="197" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C197" s="3"/>
+    </row>
+    <row r="198" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C198" s="3"/>
+    </row>
+    <row r="199" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C199" s="3"/>
+    </row>
+    <row r="200" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C200" s="3"/>
+    </row>
+    <row r="201" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C201" s="3"/>
+    </row>
+    <row r="202" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C202" s="3"/>
+    </row>
+    <row r="203" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C203" s="3"/>
+    </row>
+    <row r="204" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C204" s="3"/>
+    </row>
+    <row r="205" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C205" s="3"/>
+    </row>
+    <row r="206" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C206" s="3"/>
+    </row>
+    <row r="207" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C207" s="3"/>
+    </row>
+    <row r="208" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C208" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -937,12 +1865,23 @@
     <hyperlink ref="B7" r:id="rId6" xr:uid="{00BAFE1A-9B40-4F6E-8345-3A626BDFAAC1}"/>
     <hyperlink ref="B8" r:id="rId7" xr:uid="{C2E9AD3F-53C8-4BE5-9C2D-1889EFA7C180}"/>
     <hyperlink ref="B9" r:id="rId8" xr:uid="{67B54AA8-877C-4EAC-896C-2CC3FDF87DDE}"/>
-    <hyperlink ref="B21" r:id="rId9" xr:uid="{4A9BD8E5-C796-4122-891A-628673EF3FB7}"/>
-    <hyperlink ref="B20" r:id="rId10" xr:uid="{B9D7C85B-D9A8-4957-8EDE-C751622A6D70}"/>
+    <hyperlink ref="B24" r:id="rId9" xr:uid="{4A9BD8E5-C796-4122-891A-628673EF3FB7}"/>
+    <hyperlink ref="B23" r:id="rId10" xr:uid="{B9D7C85B-D9A8-4957-8EDE-C751622A6D70}"/>
     <hyperlink ref="B11" r:id="rId11" xr:uid="{3D133E37-B163-441B-A67C-92BA8EE0CE4C}"/>
     <hyperlink ref="B10" r:id="rId12" xr:uid="{0564751A-A291-4356-BF85-D3CB3B358724}"/>
-    <hyperlink ref="B12" r:id="rId13" xr:uid="{5D344AE8-D80C-48CE-B721-96FF13589EF5}"/>
-    <hyperlink ref="B13" r:id="rId14" xr:uid="{1933D47A-642E-468E-9166-4D85EAE30B56}"/>
+    <hyperlink ref="B13" r:id="rId13" xr:uid="{5D344AE8-D80C-48CE-B721-96FF13589EF5}"/>
+    <hyperlink ref="B14" r:id="rId14" xr:uid="{1933D47A-642E-468E-9166-4D85EAE30B56}"/>
+    <hyperlink ref="B21" r:id="rId15" xr:uid="{EE37286A-2986-464A-96E2-4B6B504D3897}"/>
+    <hyperlink ref="B20" r:id="rId16" xr:uid="{4C8F98CE-6332-4C35-90D3-5C56042039CE}"/>
+    <hyperlink ref="B22" r:id="rId17" xr:uid="{E00789BA-6F87-4D6C-9032-A99F51ADCECE}"/>
+    <hyperlink ref="B19" r:id="rId18" xr:uid="{169CC66D-5B79-43FE-B4CC-EB560D987D0D}"/>
+    <hyperlink ref="B15" r:id="rId19" xr:uid="{C9968552-2F56-4387-B67C-9456D0B1B8F5}"/>
+    <hyperlink ref="B16" r:id="rId20" xr:uid="{3A05F073-FA71-44C2-A359-7FF1C3C05FA3}"/>
+    <hyperlink ref="B17" r:id="rId21" xr:uid="{9EB2ECBA-0896-4A2D-A846-919E3D93D7D0}"/>
+    <hyperlink ref="B18" r:id="rId22" xr:uid="{9AA77F51-8866-4451-A8D0-289F15779F7A}"/>
+    <hyperlink ref="B26" r:id="rId23" xr:uid="{283C73C6-BEB6-47FD-90FA-B77CD5288D3D}"/>
+    <hyperlink ref="B12" r:id="rId24" xr:uid="{E275147C-CC28-4F86-BF71-516213A36C4A}"/>
+    <hyperlink ref="B25" r:id="rId25" xr:uid="{B287A11D-4DE0-45E4-9C85-C80087190F10}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/images/products/list_products.xlsx
+++ b/public/images/products/list_products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Claude\Projects\biohacker-digital\public\images\products\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F00DAEB-1A74-49DC-A810-C7597D21BFAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7318DD5D-6585-417E-A94B-35F264BE14C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57492" yWindow="72" windowWidth="29016" windowHeight="15696" xr2:uid="{96CA0E1B-D343-4270-BA77-1A4585D27D3C}"/>
   </bookViews>
@@ -786,6 +786,7 @@
   <dimension ref="A1:G208"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="36.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="50.6640625" style="1" customWidth="1"/>
@@ -795,7 +796,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -815,7 +816,7 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -835,7 +836,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -855,7 +856,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -875,7 +876,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -895,7 +896,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="144" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -915,7 +916,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -935,7 +936,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -955,7 +956,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -973,7 +974,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -993,7 +994,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1013,6 +1014,9 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
       <c r="B12" s="2" t="s">
         <v>103</v>
       </c>
@@ -1030,8 +1034,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>11</v>
+      <c r="A13" s="1">
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>52</v>
@@ -1050,8 +1054,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>12</v>
+      <c r="A14" s="1">
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>57</v>
@@ -1070,8 +1074,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>13</v>
+      <c r="A15" s="1">
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>83</v>
@@ -1090,8 +1094,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>14</v>
+      <c r="A16" s="1">
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>88</v>
@@ -1110,8 +1114,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>15</v>
+      <c r="A17" s="1">
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>90</v>
@@ -1130,8 +1134,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>16</v>
+      <c r="A18" s="1">
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>96</v>
@@ -1150,8 +1154,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>17</v>
+      <c r="A19" s="1">
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>80</v>
@@ -1170,8 +1174,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>18</v>
+      <c r="A20" s="1">
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>72</v>
@@ -1190,8 +1194,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>19</v>
+      <c r="A21" s="1">
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>68</v>
@@ -1210,8 +1214,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>20</v>
+      <c r="A22" s="1">
+        <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>75</v>
@@ -1230,8 +1234,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>21</v>
+      <c r="A23" s="1">
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>40</v>
@@ -1250,8 +1254,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>22</v>
+      <c r="A24" s="1">
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>36</v>
@@ -1270,8 +1274,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>23</v>
+      <c r="A25" s="1">
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>107</v>
@@ -1290,8 +1294,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>24</v>
+      <c r="A26" s="1">
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>100</v>

--- a/public/images/products/list_products.xlsx
+++ b/public/images/products/list_products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar\Claude\Projects\biohacker-digital\public\images\products\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7318DD5D-6585-417E-A94B-35F264BE14C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6074F39D-2ED3-47FE-9F8F-5FEDD1D22912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57492" yWindow="72" windowWidth="29016" windowHeight="15696" xr2:uid="{96CA0E1B-D343-4270-BA77-1A4585D27D3C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="157">
   <si>
     <t>id</t>
   </si>
@@ -234,16 +234,10 @@
     <t>category</t>
   </si>
   <si>
-    <t>Downsing</t>
-  </si>
-  <si>
     <t>Grounding</t>
   </si>
   <si>
     <t>7.83Hz Frequency Generator For Healing, Adjustable 0.1HZ-100000Hz Sine Signals Generator, USB Schumann Wave Resonance Generator, Pulses Generator Frequency Devices Sound Frequency Machine (Green)</t>
-  </si>
-  <si>
-    <t>Generator Frequency</t>
   </si>
   <si>
     <t>EMF</t>
@@ -393,6 +387,156 @@
   </si>
   <si>
     <t>RechargeableEMFMeter.jpg</t>
+  </si>
+  <si>
+    <t>Dowsing</t>
+  </si>
+  <si>
+    <t>Pendulum</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B01MQJREAI</t>
+  </si>
+  <si>
+    <t>Pendulum Made of Natural Gemstone Crystals for Dowsing Divination Chakra Reiki. Pointed with Chain and Jewelry Pouch</t>
+  </si>
+  <si>
+    <t>A gemstone pendulum made of quartz crystal. A great tool for divinations, dowsings and communicating with the spirit world.
+Dimensions: 35 x 18mm. Chain length: 18cm.</t>
+  </si>
+  <si>
+    <t>CristalPendulum.jpg</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B07DTJL8CB</t>
+  </si>
+  <si>
+    <t>4 Ring Plate Copper Metal Chamber Pendulum for Healing Care.</t>
+  </si>
+  <si>
+    <t>Benefits : Feeling better,Spiritual growth,transform life, improve abilities,Spiritual and psychological growth,</t>
+  </si>
+  <si>
+    <t>Pendulum1.jpg</t>
+  </si>
+  <si>
+    <t>Grounding Tester Kit, Conductivity Test Pen &amp; Outlet Continuity Tester Electrical Ground Product Test Kit for Mat Pads Sheets Pillow Cases Electric Blankets Wristband Accessories</t>
+  </si>
+  <si>
+    <t>Product Included: You will receive a comprehensive grounding product test kit, including 1 conductivity test pen and 1 outlet tester, designed to ensure the safety and effectiveness of your grounding products.
+Premium Material: Crafted with premium-quality plastic and copper, which are not easy to break and wear, ensuring accuracy, durability and reliability in every test.</t>
+  </si>
+  <si>
+    <t>OutletTester2.jpg</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0FNMY6SSX</t>
+  </si>
+  <si>
+    <t>Electroculture</t>
+  </si>
+  <si>
+    <t>Electroculture Copper Gardening Antenna, Copper Wire for Gardening Garden Plant Stakes Pure Coppers Rods for Garden Electro Culture Coppers Coils Tools Pyramid Tensor Rings Kit (6Pcs,43cm)</t>
+  </si>
+  <si>
+    <t>Electroculture plant stakes is a method of using conductive metals, harness the earth's natural energy to the soil, significantly increasing plant growth, while reduce irrigation, not only increases the yields of your crops but also reduces the need for fertilizers
+Electroculture copper gardening Antenna uses 99.9% copper wires to be wound clockwise onto wooden sticks. are placed into the soil to create an ether antenna,ensures good conductivity and durability</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0H3ZD7SGQ</t>
+  </si>
+  <si>
+    <t>Electroculture1.jpg</t>
+  </si>
+  <si>
+    <t>Advanced Plant Growth Principles: 12/17inches electroculture copper gardening antennas optimizes plant vitality and growth environment through the energy of nature, improves the energy and overall quality required for the growth of plants, vegetables, etc.
+High Premium Garden Copper Stakes: Indoor copper wire for plants features with 30/43cm natural woods and 99.9% pure solid copper wire. Electroculture plant stakes can utilize magnetic fields to obtain more energy for plants with excellent long-term conductivity and durability.</t>
+  </si>
+  <si>
+    <t>Electroculture2.jpg</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0H4YXWKLS</t>
+  </si>
+  <si>
+    <t>3 Pack Electroculture Copper Gardening Antenna Kit Thick 10-Gauge 99% Copper Wire Electroculture Plant Stakes Tensor Rings Kit Rods Electronic Planting for Growing Vegetable Garden Plants Support</t>
+  </si>
+  <si>
+    <t>Harness Natural Earth Energy: Stimulate stronger roots and increase yields with electroculture copper gardening antenna. This copper gardening antenna kit can enhances plant vibrancy. Our design draws on tesla coil principles for optimal energy flow
+Superior 10-Gauge Pure Copper: Crafted from precision-wound copper coil wire antennas, these copper rods electronic planting tools maximize energy transmission. Enjoy healthier roots and abundant growth in garden beds, raised planters, or indoor pots</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0GL8FM7M6</t>
+  </si>
+  <si>
+    <t>Electroculture3.jpg</t>
+  </si>
+  <si>
+    <t>2PCS Coil Winding Jig, Copper Wire Antenna Jig Spiral Antenna Make Cones Air Plant Holder Tool Vegetables Garden Tool for Electroculture Gardening</t>
+  </si>
+  <si>
+    <t>Versatile Gardening Tool: The electroculture coils making jig is designed for crafting precise spirals and cones, ideal for copper gardening antenna making tool projects. Its adjustable design accommodates various wire gauges, making it a must-have for garden tools enthusiasts. Easily create fibonacci coil winding jig patterns to enhance plant growth ﻿
+Precision Spiral Creation: With the gardening wire antenna jig, achieve consistent spirals for antenna jig making tool applications. The coil winding jig ensures uniform loops, great for copper wire winding jig projects. Its sturdy build guarantees smooth operation every time ﻿</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0FHYPT8B5</t>
+  </si>
+  <si>
+    <t>Electroculture4.jpg</t>
+  </si>
+  <si>
+    <t>TENS Machine</t>
+  </si>
+  <si>
+    <t>DR-HO'S Neck Pain Pro Ultimate Package - TENS &amp; EMS Therapy to Relieve Neck and Shoulder Pain</t>
+  </si>
+  <si>
+    <t>TENS_Dr-Ho.jpg</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B079Q4NWBT</t>
+  </si>
+  <si>
+    <t>DR-HO’S devices are developed by Dr. Michael Ho who has used his education and clinical experiences in treating patients to develop a line of home healthcare products that are effective for relieving pain. For over 35 years, he has helped many people live happier, more active life with less pain.</t>
+  </si>
+  <si>
+    <t>AUVON Dual Channel TENS EMS Unit 24 Modes Muscle Stimulator for Pain Relief, Rechargeable TENS Machine Massager with 12 Pads, ABS Pads Holder, USB Cable and Dust-Proof Storage Bag</t>
+  </si>
+  <si>
+    <t>TENS + EMS COMBINATION UNIT. AUVON TENS &amp; PMS / EMS device combines 2 therapies in 1 device, in which TENS provides safe, non-invasive, drug-free methods of pain relief used by doctors and physical therapists for years. PMS / EMS brings elicitation of muscle contraction using electrical impulses and activates the muscles to assist in the increase of strength and endurance as a rehab and strength training tool.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B085TL8TPJ</t>
+  </si>
+  <si>
+    <t>TENS_Machine.jpg</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Tuning Forks for Healing Set, Includes 128Hz, 136Hz, 256Hz, 384Hz, Weighted &amp; Unweighted Tuning Forks Set with Reflex Hammer, Activator, Gem feet, for Sound Therapy, Chakra, Yoga, Meditation</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0FN438K9M</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EXTENDED VIBRATION &amp; PREMIUM ALLOY – Crafted from high-quality, non-magnetic aluminum alloy, these instruments are impact-resistant and lighter than steel alternatives. The material ensures a pure tone with a long sustain time. Most importantly, each fork undergoes rigorous testing to guarantee frequency accuracy, making them reliable tools for sensory vibration testing, energy tuning concepts, and professional sound therapy sessions where precision is paramount.</t>
+  </si>
+  <si>
+    <t>Frequency1.jpg</t>
+  </si>
+  <si>
+    <t>Portable Electronic Tibetan Singing Bowl, 8 Healing Frequencies (369-963Hz), Auto/Manual Mode, Vibration &amp; Timer - USB-C Rechargeable Meditation Device for Yoga, Relaxation, Reiki, Best Gift Choice</t>
+  </si>
+  <si>
+    <t>Frequency2.jpg</t>
+  </si>
+  <si>
+    <t>【Digital Tibetan Singing Bowl Experience】: Authentic meditation companion, sound healing device. This electronic Singing Bowl replicates sacred tibetan singing bowl. Designed specifically for meditation practitioners, it delivers immersive sound therapy without physical bowls. Instantly create serene atmospheres for yoga studios, therapy sessions, or personal mindfulness practice. Portable solution for modern spiritual seekers.</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/dp/B0FDX3JSMQ</t>
   </si>
 </sst>
 </file>
@@ -783,10 +927,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92ADB5C5-5056-4759-9A16-E445611996FF}">
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:H208"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="3.77734375" style="1" customWidth="1"/>
     <col min="2" max="2" width="36.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="50.6640625" style="1" customWidth="1"/>
@@ -795,7 +939,7 @@
     <col min="7" max="7" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -814,38 +958,40 @@
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -854,18 +1000,19 @@
       <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -874,509 +1021,729 @@
       <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>15</v>
+      <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>62</v>
+      <c r="B8" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="3"/>
+      <c r="B9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="F9" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>43</v>
+        <v>150</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>149</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>44</v>
+        <v>151</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>104</v>
+        <v>156</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>105</v>
+        <v>155</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>53</v>
+      <c r="B13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>55</v>
+      <c r="B14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>82</v>
+      <c r="B15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>87</v>
+      <c r="B16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>92</v>
+      <c r="B17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>95</v>
+      <c r="B18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>79</v>
+      <c r="E19" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>70</v>
+      <c r="B20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>66</v>
+      <c r="B21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>77</v>
+      <c r="B22" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>39</v>
+        <v>126</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>35</v>
+        <v>130</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+      <c r="H24" s="1"/>
+    </row>
+    <row r="25" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>64</v>
+        <v>133</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>108</v>
+        <v>131</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H26" s="1"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C32" s="3"/>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C34" s="3"/>
-    </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C35" s="3"/>
-    </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C36" s="3"/>
-    </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C37" s="3"/>
-    </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C38" s="3"/>
     </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C39" s="3"/>
     </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C40" s="3"/>
     </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C41" s="3"/>
     </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C42" s="3"/>
     </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C43" s="3"/>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C44" s="3"/>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C45" s="3"/>
     </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C46" s="3"/>
     </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C47" s="3"/>
     </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C48" s="3"/>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.3">
@@ -1861,31 +2228,15 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{25C8B4E5-DB19-40D0-AB58-DECE73272A86}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{1A965D54-C4EA-45F4-ACA6-4E564D476325}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{5CDE0745-B2AD-4EEC-8C9F-4047C7D6F617}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{8D2A5934-D35F-4298-A17F-3D1137EAE018}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{364445A0-34FB-4657-B12F-595AC541E726}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{00BAFE1A-9B40-4F6E-8345-3A626BDFAAC1}"/>
-    <hyperlink ref="B8" r:id="rId7" xr:uid="{C2E9AD3F-53C8-4BE5-9C2D-1889EFA7C180}"/>
-    <hyperlink ref="B9" r:id="rId8" xr:uid="{67B54AA8-877C-4EAC-896C-2CC3FDF87DDE}"/>
-    <hyperlink ref="B24" r:id="rId9" xr:uid="{4A9BD8E5-C796-4122-891A-628673EF3FB7}"/>
-    <hyperlink ref="B23" r:id="rId10" xr:uid="{B9D7C85B-D9A8-4957-8EDE-C751622A6D70}"/>
-    <hyperlink ref="B11" r:id="rId11" xr:uid="{3D133E37-B163-441B-A67C-92BA8EE0CE4C}"/>
-    <hyperlink ref="B10" r:id="rId12" xr:uid="{0564751A-A291-4356-BF85-D3CB3B358724}"/>
-    <hyperlink ref="B13" r:id="rId13" xr:uid="{5D344AE8-D80C-48CE-B721-96FF13589EF5}"/>
-    <hyperlink ref="B14" r:id="rId14" xr:uid="{1933D47A-642E-468E-9166-4D85EAE30B56}"/>
-    <hyperlink ref="B21" r:id="rId15" xr:uid="{EE37286A-2986-464A-96E2-4B6B504D3897}"/>
-    <hyperlink ref="B20" r:id="rId16" xr:uid="{4C8F98CE-6332-4C35-90D3-5C56042039CE}"/>
-    <hyperlink ref="B22" r:id="rId17" xr:uid="{E00789BA-6F87-4D6C-9032-A99F51ADCECE}"/>
-    <hyperlink ref="B19" r:id="rId18" xr:uid="{169CC66D-5B79-43FE-B4CC-EB560D987D0D}"/>
-    <hyperlink ref="B15" r:id="rId19" xr:uid="{C9968552-2F56-4387-B67C-9456D0B1B8F5}"/>
-    <hyperlink ref="B16" r:id="rId20" xr:uid="{3A05F073-FA71-44C2-A359-7FF1C3C05FA3}"/>
-    <hyperlink ref="B17" r:id="rId21" xr:uid="{9EB2ECBA-0896-4A2D-A846-919E3D93D7D0}"/>
-    <hyperlink ref="B18" r:id="rId22" xr:uid="{9AA77F51-8866-4451-A8D0-289F15779F7A}"/>
-    <hyperlink ref="B26" r:id="rId23" xr:uid="{283C73C6-BEB6-47FD-90FA-B77CD5288D3D}"/>
-    <hyperlink ref="B12" r:id="rId24" xr:uid="{E275147C-CC28-4F86-BF71-516213A36C4A}"/>
-    <hyperlink ref="B25" r:id="rId25" xr:uid="{B287A11D-4DE0-45E4-9C85-C80087190F10}"/>
+    <hyperlink ref="B37" r:id="rId1" xr:uid="{3522C7F7-3E50-47E4-9D53-FCC7C0724FD0}"/>
+    <hyperlink ref="B23" r:id="rId2" xr:uid="{B7621B65-3785-43E8-8F83-8DA46E26FCA1}"/>
+    <hyperlink ref="B24" r:id="rId3" xr:uid="{EA7C7C26-66F9-42B1-8B9A-0E1B0D0A0529}"/>
+    <hyperlink ref="B25" r:id="rId4" xr:uid="{B99449A1-9F96-4FA7-9B03-593594D23498}"/>
+    <hyperlink ref="B26" r:id="rId5" xr:uid="{59A1E795-58A9-46CD-A3E2-A83244C0AE22}"/>
+    <hyperlink ref="B27" r:id="rId6" xr:uid="{D6EF1E66-7366-4CDF-97E8-C2E308123954}"/>
+    <hyperlink ref="B28" r:id="rId7" xr:uid="{AC3F2E8B-6A82-48C3-B0E5-4594FDC57CB5}"/>
+    <hyperlink ref="B11" r:id="rId8" xr:uid="{061F099B-D3A2-464E-B51F-20097BD960DC}"/>
+    <hyperlink ref="B12" r:id="rId9" xr:uid="{C8EEEF14-A1C1-4FB3-947E-F8FB01074C25}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
